--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487197_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487197_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. CHIA SANCHEZ</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5355</v>
+        <v>-0.1944</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2371</v>
+        <v>-0.3136</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.1192</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2273</v>
+        <v>-3.0804</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3539</v>
+        <v>-3.1961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5812</v>
+        <v>0.1157</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2617</v>
+        <v>-0.3911</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0.9524</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2617</v>
+        <v>0.5612</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0344</v>
+        <v>-2.6893</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3539</v>
+        <v>-2.2437</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6805</v>
+        <v>-0.4456</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.965</v>
+        <v>2.3161</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.965</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2023</v>
+        <v>-1.2298</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0595</v>
+        <v>-0.7571</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2617</v>
+        <v>-0.4726</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. RUIZ FERNÁNDEZ</t>
+          <t>G. CHIA SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8675</v>
+        <v>-0.589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.038</v>
+        <v>0.2371</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9055</v>
+        <v>-0.8262</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5853</v>
+        <v>0.2273</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0155</v>
+        <v>-0.3539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5698</v>
+        <v>0.5812</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3355</v>
+        <v>1.2617</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3519</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0164</v>
+        <v>1.2617</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9207</v>
+        <v>-1.0344</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3674</v>
+        <v>-0.3539</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5534</v>
+        <v>-0.6805</v>
       </c>
       <c r="P3" t="n">
-        <v>0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4752</v>
+        <v>0.1487</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2974</v>
+        <v>-0.0595</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1778</v>
+        <v>0.2082</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>A. RUIZ FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.2344</v>
+        <v>-0.6335</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.193</v>
+        <v>0.1382</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0414</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.0804</v>
+        <v>-0.5853</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.1961</v>
+        <v>-0.0155</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1157</v>
+        <v>-0.5698</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3911</v>
+        <v>0.3355</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9524</v>
+        <v>0.3519</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5612</v>
+        <v>-0.0164</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6893</v>
+        <v>-0.9207</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2437</v>
+        <v>-0.3674</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4456</v>
+        <v>-0.5534</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3161</v>
+        <v>0.193</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2811</v>
+        <v>0.193</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2698</v>
+        <v>-0.2413</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6366</v>
+        <v>-0.1973</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6333</v>
+        <v>-0.044</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.999</v>
+        <v>-1.6113</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1587</v>
+        <v>-1.618</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8403</v>
+        <v>0.0067</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.2021</v>
+        <v>-2.6482</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.5399</v>
+        <v>-3.8077</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6622</v>
+        <v>1.1595</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.8196</v>
+        <v>0.0142</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.59</v>
+        <v>-1.8579</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2295</v>
+        <v>1.8722</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3825</v>
+        <v>-2.6624</v>
       </c>
       <c r="N5" t="n">
         <v>-1.9498</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4327</v>
+        <v>-0.7126</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3161</v>
+        <v>3.2811</v>
       </c>
       <c r="S5" t="n">
-        <v>0.852</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3979</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4541</v>
+        <v>0.002</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1368</v>
+        <v>-2.2584</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1971</v>
+        <v>-2.5024</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0602</v>
+        <v>0.244</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6482</v>
+        <v>-8.5085</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.8077</v>
+        <v>-5.7309</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1595</v>
+        <v>-2.7775</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0142</v>
+        <v>-5.9591</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.8579</v>
+        <v>-3.3537</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8722</v>
+        <v>-2.6054</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6624</v>
+        <v>-2.5493</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9498</v>
+        <v>-2.3772</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7126</v>
+        <v>-0.1721</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2811</v>
+        <v>3.0881</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4766</v>
+        <v>-0.7849</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5321</v>
+        <v>-0.4901</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0555</v>
+        <v>-0.2948</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3281</v>
+        <v>4.9119</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>4.9119</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7849</v>
+        <v>-2.588</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9218</v>
+        <v>-1.3996</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1369</v>
+        <v>-1.1883</v>
       </c>
       <c r="G7" t="n">
-        <v>-8.5085</v>
+        <v>-4.2021</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.7309</v>
+        <v>-2.5399</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.7775</v>
+        <v>-1.6622</v>
       </c>
       <c r="J7" t="n">
-        <v>-5.9591</v>
+        <v>-1.8196</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.3537</v>
+        <v>-0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.6054</v>
+        <v>-1.2295</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5493</v>
+        <v>-2.3825</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3772</v>
+        <v>-1.9498</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1721</v>
+        <v>-0.4327</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0881</v>
+        <v>2.3161</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3114</v>
+        <v>0.2631</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9095</v>
+        <v>0.157</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4019</v>
+        <v>0.1061</v>
       </c>
       <c r="V7" t="n">
-        <v>4.9119</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.9119</v>
+        <v>1.228</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7992</v>
+        <v>-2.8993</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7226</v>
+        <v>-1.8227</v>
       </c>
       <c r="F8" t="n">
         <v>-1.0766</v>
@@ -1078,10 +1078,10 @@
         <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3411</v>
+        <v>0.2409</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4442</v>
+        <v>0.3441</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1031</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8967</v>
+        <v>-4.2206</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6161</v>
+        <v>-3.7155</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2806</v>
+        <v>-0.5052</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7828</v>
+        <v>-5.2176</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0523</v>
+        <v>-2.1145</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7305</v>
+        <v>-3.1031</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6131</v>
+        <v>-3.2759</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7351</v>
+        <v>-1.2731</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>-2.0028</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1697</v>
+        <v>-1.9417</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.3172</v>
+        <v>-0.8414</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8526</v>
+        <v>-1.1003</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.0881</v>
+        <v>1.5441</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.7902</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7021</v>
+        <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1323</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3313</v>
+        <v>-0.4395</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.199</v>
+        <v>-0.192</v>
       </c>
       <c r="V9" t="n">
-        <v>1.842</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.614</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5667</v>
+        <v>-5.1003</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0347</v>
+        <v>-3.7394</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5319</v>
+        <v>-1.3609</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.2176</v>
+        <v>-3.7828</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1145</v>
+        <v>-3.0523</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.1031</v>
+        <v>-0.7305</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.2759</v>
+        <v>-0.6131</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2731</v>
+        <v>-0.7351</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0028</v>
+        <v>0.1221</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9417</v>
+        <v>-3.1697</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8414</v>
+        <v>-2.3172</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1003</v>
+        <v>-0.8526</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5441</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-5.7902</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5441</v>
+        <v>2.7021</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9776</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7588</v>
+        <v>0.2079</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2188</v>
+        <v>-0.2793</v>
       </c>
       <c r="V10" t="n">
-        <v>0.08450000000000001</v>
+        <v>1.842</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X10" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.744</v>
+        <v>-5.5774</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.606</v>
+        <v>-4.5466</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1379</v>
+        <v>-1.0308</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9493</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4785</v>
+        <v>-0.312</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4164</v>
+        <v>-0.3569</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0621</v>
+        <v>0.0449</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-26.5647</v>
+        <v>-25.6722</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.1749</v>
+        <v>-19.2825</v>
       </c>
       <c r="F12" t="n">
         <v>-6.3898</v>
@@ -1390,13 +1390,13 @@
         <v>17.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.4614</v>
+        <v>-3.5694</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4369</v>
+        <v>-2.5445</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0247</v>
+        <v>-1.0246</v>
       </c>
       <c r="V12" t="n">
         <v>8.31</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.439</v>
+        <v>10.7599</v>
       </c>
       <c r="E13" t="n">
         <v>6.496</v>
       </c>
       <c r="F13" t="n">
-        <v>3.943</v>
+        <v>4.2639</v>
       </c>
       <c r="G13" t="n">
         <v>8.441800000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>0.897</v>
+        <v>1.2179</v>
       </c>
       <c r="T13" t="n">
         <v>0.0278</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8692</v>
+        <v>1.1901</v>
       </c>
       <c r="V13" t="n">
         <v>0.3281</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0821</v>
+        <v>4.5332</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2285</v>
+        <v>0.0282</v>
       </c>
       <c r="F14" t="n">
-        <v>4.8537</v>
+        <v>4.505</v>
       </c>
       <c r="G14" t="n">
         <v>4.4017</v>
@@ -1546,13 +1546,13 @@
         <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3247</v>
+        <v>1.7757</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5169</v>
+        <v>0.3166</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8077</v>
+        <v>1.4591</v>
       </c>
       <c r="V14" t="n">
         <v>0.2859</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5526</v>
+        <v>3.9522</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1763</v>
+        <v>0.3521</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3763</v>
+        <v>3.6001</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5215</v>
+        <v>2.7935</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9124</v>
+        <v>1.6789</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6091</v>
+        <v>1.1146</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3997</v>
+        <v>1.1109</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3183</v>
+        <v>0.5175</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0814</v>
+        <v>0.5934</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1218</v>
+        <v>1.6826</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5941</v>
+        <v>1.1614</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5212</v>
       </c>
       <c r="P15" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5552</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2234</v>
+        <v>0.2062</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3318</v>
+        <v>0.5664</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2298</v>
+        <v>3.7667</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3521</v>
+        <v>2.1763</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8777</v>
+        <v>1.5904</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7935</v>
+        <v>3.5215</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6789</v>
+        <v>2.9124</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1146</v>
+        <v>0.6091</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1109</v>
+        <v>2.3997</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5175</v>
+        <v>2.3183</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5934</v>
+        <v>0.0814</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6826</v>
+        <v>1.1218</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1614</v>
+        <v>0.5941</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5212</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0502</v>
+        <v>-0.3411</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2062</v>
+        <v>-0.2234</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.156</v>
+        <v>-0.1177</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7966</v>
+        <v>2.0942</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7010999999999999</v>
+        <v>2.2928</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0955</v>
+        <v>-0.1985</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7815</v>
+        <v>3.169</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6612</v>
+        <v>1.6125</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1203</v>
+        <v>1.5566</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6865</v>
+        <v>2.3942</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3609</v>
+        <v>1.0918</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3256</v>
+        <v>1.3024</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0949</v>
+        <v>0.7748</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3002</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7947</v>
+        <v>0.2542</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5712</v>
+        <v>0.1229</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6009</v>
+        <v>-0.1014</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.2244</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1701</v>
+        <v>-2.7418</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5138</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9548</v>
+        <v>2.0826</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9923</v>
+        <v>-0.013</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0376</v>
+        <v>2.0956</v>
       </c>
       <c r="G18" t="n">
-        <v>3.169</v>
+        <v>3.5173</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6125</v>
+        <v>2.4384</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5566</v>
+        <v>1.0789</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3942</v>
+        <v>2.0417</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0918</v>
+        <v>2.0181</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3024</v>
+        <v>0.0236</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7748</v>
+        <v>1.4757</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4203</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2542</v>
+        <v>1.0553</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0165</v>
+        <v>0.6352</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4019</v>
+        <v>-0.1246</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3853</v>
+        <v>0.7598</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.7418</v>
+        <v>-2.4559</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7418</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3145</v>
+        <v>1.8217</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5137</v>
+        <v>-0.3003</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8282</v>
+        <v>2.1219</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5173</v>
+        <v>2.7815</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4384</v>
+        <v>1.6612</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0789</v>
+        <v>1.1203</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0417</v>
+        <v>1.6865</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0181</v>
+        <v>1.3609</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0236</v>
+        <v>0.3256</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4757</v>
+        <v>1.0949</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4203</v>
+        <v>0.3002</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0553</v>
+        <v>0.7947</v>
       </c>
       <c r="P19" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1329</v>
+        <v>1.5963</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6253</v>
+        <v>0.5995</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4924</v>
+        <v>0.9967</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4559</v>
+        <v>-2.1701</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4559</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8635</v>
+        <v>0.6896</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6927</v>
+        <v>0.4924</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1708</v>
+        <v>0.1972</v>
       </c>
       <c r="G20" t="n">
         <v>4.2137</v>
@@ -2014,13 +2014,13 @@
         <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>0.271</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3847</v>
+        <v>0.1844</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1137</v>
+        <v>-0.0873</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8842</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3266</v>
+        <v>0.2856</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0459</v>
+        <v>-0.8457</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3725</v>
+        <v>1.1313</v>
       </c>
       <c r="G21" t="n">
         <v>0.6188</v>
@@ -2092,13 +2092,13 @@
         <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0529</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1785</v>
+        <v>0.0218</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2723</v>
+        <v>0.031</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9948</v>
+        <v>-2.0859</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6895</v>
+        <v>-4.2889</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6947</v>
+        <v>2.203</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1508</v>
@@ -2170,13 +2170,13 @@
         <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0417</v>
+        <v>-0.1329</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2829</v>
+        <v>0.1177</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7588</v>
+        <v>-0.2505</v>
       </c>
       <c r="V22" t="n">
         <v>0.8999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>26.5647</v>
+        <v>27.8998</v>
       </c>
       <c r="E23" t="n">
-        <v>6.3899</v>
+        <v>6.389899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>20.1748</v>
+        <v>21.5099</v>
       </c>
       <c r="G23" t="n">
         <v>33.30800000000001</v>
@@ -2248,13 +2248,13 @@
         <v>14.4756</v>
       </c>
       <c r="S23" t="n">
-        <v>4.461600000000001</v>
+        <v>5.796799999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0245</v>
+        <v>1.0246</v>
       </c>
       <c r="U23" t="n">
-        <v>3.436900000000001</v>
+        <v>4.772</v>
       </c>
       <c r="V23" t="n">
         <v>-8.309800000000001</v>
